--- a/评测/问答评测明细.xlsx
+++ b/评测/问答评测明细.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="657">
   <si>
     <t>编号</t>
   </si>
@@ -1652,6 +1652,12 @@
   </si>
   <si>
     <t>这是部门规章的要求。《证券期货投资者适当性管理办法》第二十七条明确规定，委托方不提供规定信息或提供不完整的，经营机构应当拒绝代销产品或者提供服务；该办法问答（片段4）进一步确认此义务，并强调经营机构须自行调查核实、履行适当性匹配义务。因此，若客户不配合提供适当性信息，经营机构继续提供服务即违反该部门规章。</t>
+  </si>
+  <si>
+    <t>引用错误</t>
+  </si>
+  <si>
+    <t>问“客户不配合提供适当性信息怎么办”，参考答案是第三十三条：告知后果并拒绝销售。系统引用的是第二十七条（委托方不提供信息拒绝代销），这是代销场景，不是一般客户不配合的场景。</t>
   </si>
   <si>
     <t>D6-07</t>
@@ -2920,12 +2926,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -7071,24 +7080,27 @@
         <v>437</v>
       </c>
       <c r="Q82" t="s">
-        <v>31</v>
+        <v>457</v>
+      </c>
+      <c r="R82" s="3" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="83" ht="409.5" spans="1:18">
       <c r="A83" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B83" t="s">
         <v>427</v>
       </c>
       <c r="C83" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D83" t="s">
         <v>21</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F83" t="s">
         <v>23</v>
@@ -7103,33 +7115,33 @@
         <v>444</v>
       </c>
       <c r="K83" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L83" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M83">
         <v>2</v>
       </c>
       <c r="O83" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="Q83" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R83" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="84" ht="409.5" spans="1:18">
       <c r="A84" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B84" t="s">
         <v>427</v>
       </c>
       <c r="C84" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D84" t="s">
         <v>21</v>
@@ -7150,10 +7162,10 @@
         <v>133</v>
       </c>
       <c r="K84" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L84" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M84">
         <v>2</v>
@@ -7167,19 +7179,19 @@
     </row>
     <row r="85" spans="1:18">
       <c r="A85" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B85" t="s">
         <v>427</v>
       </c>
       <c r="C85" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D85" t="s">
         <v>21</v>
       </c>
       <c r="E85" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F85" t="s">
         <v>23</v>
@@ -7197,7 +7209,7 @@
         <v>435</v>
       </c>
       <c r="L85" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M85">
         <v>2</v>
@@ -7211,19 +7223,19 @@
     </row>
     <row r="86" ht="409.5" spans="1:18">
       <c r="A86" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B86" t="s">
         <v>427</v>
       </c>
       <c r="C86" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D86" t="s">
         <v>21</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F86" t="s">
         <v>23</v>
@@ -7238,10 +7250,10 @@
         <v>27</v>
       </c>
       <c r="K86" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L86" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M86">
         <v>1</v>
@@ -7255,13 +7267,13 @@
     </row>
     <row r="87" ht="409.5" spans="1:18">
       <c r="A87" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B87" t="s">
         <v>427</v>
       </c>
       <c r="C87" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D87" t="s">
         <v>21</v>
@@ -7282,13 +7294,13 @@
         <v>27</v>
       </c>
       <c r="L87" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M87">
         <v>4</v>
       </c>
       <c r="O87" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="Q87" t="s">
         <v>31</v>
@@ -7296,19 +7308,19 @@
     </row>
     <row r="88" ht="409.5" spans="1:18">
       <c r="A88" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B88" t="s">
         <v>427</v>
       </c>
       <c r="C88" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D88" t="s">
         <v>21</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F88" t="s">
         <v>23</v>
@@ -7323,10 +7335,10 @@
         <v>27</v>
       </c>
       <c r="K88" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L88" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M88">
         <v>2</v>
@@ -7340,19 +7352,19 @@
     </row>
     <row r="89" spans="1:18">
       <c r="A89" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B89" t="s">
         <v>427</v>
       </c>
       <c r="C89" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D89" t="s">
         <v>21</v>
       </c>
       <c r="E89" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F89" t="s">
         <v>23</v>
@@ -7367,16 +7379,16 @@
         <v>27</v>
       </c>
       <c r="K89" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L89" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M89">
         <v>3</v>
       </c>
       <c r="O89" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q89" t="s">
         <v>31</v>
@@ -7384,19 +7396,19 @@
     </row>
     <row r="90" ht="409.5" spans="1:18">
       <c r="A90" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s">
         <v>427</v>
       </c>
       <c r="C90" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D90" t="s">
         <v>21</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F90" t="s">
         <v>23</v>
@@ -7414,7 +7426,7 @@
         <v>186</v>
       </c>
       <c r="L90" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M90">
         <v>3</v>
@@ -7428,19 +7440,19 @@
     </row>
     <row r="91" spans="1:18">
       <c r="A91" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B91" t="s">
         <v>427</v>
       </c>
       <c r="C91" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D91" t="s">
         <v>21</v>
       </c>
       <c r="E91" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F91" t="s">
         <v>23</v>
@@ -7455,10 +7467,10 @@
         <v>133</v>
       </c>
       <c r="K91" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L91" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M91">
         <v>1</v>
@@ -7472,19 +7484,19 @@
     </row>
     <row r="92" ht="409.5" spans="1:18">
       <c r="A92" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B92" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C92" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D92" t="s">
         <v>126</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F92" t="s">
         <v>23</v>
@@ -7496,19 +7508,19 @@
         <v>178</v>
       </c>
       <c r="I92" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J92" t="s">
         <v>27</v>
       </c>
       <c r="L92" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="M92">
         <v>4</v>
       </c>
       <c r="O92" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="Q92" t="s">
         <v>31</v>
@@ -7516,13 +7528,13 @@
     </row>
     <row r="93" ht="409.5" spans="1:18">
       <c r="A93" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B93" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C93" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D93" t="s">
         <v>21</v>
@@ -7546,7 +7558,7 @@
         <v>86</v>
       </c>
       <c r="L93" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M93">
         <v>1</v>
@@ -7560,19 +7572,19 @@
     </row>
     <row r="94" spans="1:18">
       <c r="A94" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B94" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C94" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D94" t="s">
         <v>126</v>
       </c>
       <c r="E94" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F94" t="s">
         <v>23</v>
@@ -7584,19 +7596,19 @@
         <v>178</v>
       </c>
       <c r="I94" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J94" t="s">
         <v>27</v>
       </c>
       <c r="L94" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M94">
         <v>3</v>
       </c>
       <c r="O94" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Q94" t="s">
         <v>31</v>
@@ -7604,19 +7616,19 @@
     </row>
     <row r="95" spans="1:18">
       <c r="A95" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B95" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C95" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D95" t="s">
         <v>126</v>
       </c>
       <c r="E95" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F95" t="s">
         <v>23</v>
@@ -7628,19 +7640,19 @@
         <v>178</v>
       </c>
       <c r="I95" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J95" t="s">
         <v>27</v>
       </c>
       <c r="L95" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M95">
         <v>3</v>
       </c>
       <c r="O95" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="Q95" t="s">
         <v>31</v>
@@ -7648,19 +7660,19 @@
     </row>
     <row r="96" ht="409.5" spans="1:18">
       <c r="A96" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B96" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C96" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D96" t="s">
         <v>126</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F96" t="s">
         <v>23</v>
@@ -7678,7 +7690,7 @@
         <v>27</v>
       </c>
       <c r="L96" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="M96">
         <v>2</v>
@@ -7692,13 +7704,13 @@
     </row>
     <row r="97" spans="1:18">
       <c r="A97" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B97" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C97" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D97" t="s">
         <v>126</v>
@@ -7716,19 +7728,19 @@
         <v>178</v>
       </c>
       <c r="I97" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J97" t="s">
         <v>27</v>
       </c>
       <c r="L97" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M97">
         <v>2</v>
       </c>
       <c r="O97" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="Q97" t="s">
         <v>31</v>
@@ -7736,13 +7748,13 @@
     </row>
     <row r="98" ht="409.5" spans="1:18">
       <c r="A98" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B98" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C98" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D98" t="s">
         <v>126</v>
@@ -7760,19 +7772,19 @@
         <v>178</v>
       </c>
       <c r="I98" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J98" t="s">
         <v>27</v>
       </c>
       <c r="L98" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M98">
         <v>3</v>
       </c>
       <c r="O98" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="Q98" t="s">
         <v>31</v>
@@ -7780,19 +7792,19 @@
     </row>
     <row r="99" spans="1:18">
       <c r="A99" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B99" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C99" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D99" t="s">
         <v>126</v>
       </c>
       <c r="E99" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F99" t="s">
         <v>23</v>
@@ -7804,16 +7816,16 @@
         <v>178</v>
       </c>
       <c r="I99" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J99" t="s">
         <v>27</v>
       </c>
       <c r="K99" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L99" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M99">
         <v>2</v>
@@ -7827,19 +7839,19 @@
     </row>
     <row r="100" ht="409.5" spans="1:18">
       <c r="A100" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B100" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C100" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D100" t="s">
         <v>126</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F100" t="s">
         <v>23</v>
@@ -7851,13 +7863,13 @@
         <v>178</v>
       </c>
       <c r="I100" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J100" t="s">
         <v>27</v>
       </c>
       <c r="L100" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="M100">
         <v>2</v>
@@ -7871,19 +7883,19 @@
     </row>
     <row r="101" spans="1:18">
       <c r="A101" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C101" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D101" t="s">
         <v>126</v>
       </c>
       <c r="E101" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="F101" t="s">
         <v>23</v>
@@ -7895,22 +7907,22 @@
         <v>178</v>
       </c>
       <c r="I101" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J101" t="s">
         <v>27</v>
       </c>
       <c r="K101" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="L101" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M101">
         <v>2</v>
       </c>
       <c r="O101" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Q101" t="s">
         <v>31</v>
@@ -7918,19 +7930,19 @@
     </row>
     <row r="102" ht="409.5" spans="1:18">
       <c r="A102" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C102" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D102" t="s">
         <v>126</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="F102" t="s">
         <v>23</v>
@@ -7942,13 +7954,13 @@
         <v>178</v>
       </c>
       <c r="I102" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J102" t="s">
         <v>27</v>
       </c>
       <c r="L102" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M102">
         <v>1</v>
@@ -7960,24 +7972,24 @@
         <v>416</v>
       </c>
       <c r="R102" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="103" ht="409.5" spans="1:18">
       <c r="A103" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B103" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C103" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D103" t="s">
         <v>126</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F103" t="s">
         <v>23</v>
@@ -7989,19 +8001,19 @@
         <v>178</v>
       </c>
       <c r="I103" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J103" t="s">
         <v>27</v>
       </c>
       <c r="L103" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="M103">
         <v>2</v>
       </c>
       <c r="O103" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="Q103" t="s">
         <v>31</v>
@@ -8009,19 +8021,19 @@
     </row>
     <row r="104" spans="1:18">
       <c r="A104" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B104" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C104" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D104" t="s">
         <v>126</v>
       </c>
       <c r="E104" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F104" t="s">
         <v>23</v>
@@ -8033,13 +8045,13 @@
         <v>178</v>
       </c>
       <c r="I104" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J104" t="s">
         <v>27</v>
       </c>
       <c r="L104" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M104">
         <v>2</v>
@@ -8053,19 +8065,19 @@
     </row>
     <row r="105" ht="409.5" spans="1:18">
       <c r="A105" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B105" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C105" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D105" t="s">
         <v>126</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F105" t="s">
         <v>23</v>
@@ -8077,22 +8089,22 @@
         <v>178</v>
       </c>
       <c r="I105" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J105" t="s">
         <v>27</v>
       </c>
       <c r="K105" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L105" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M105">
         <v>2</v>
       </c>
       <c r="O105" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="Q105" t="s">
         <v>31</v>
@@ -8100,19 +8112,19 @@
     </row>
     <row r="106" ht="409.5" spans="1:18">
       <c r="A106" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B106" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C106" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D106" t="s">
         <v>126</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F106" t="s">
         <v>23</v>
@@ -8124,19 +8136,19 @@
         <v>178</v>
       </c>
       <c r="I106" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J106" t="s">
         <v>27</v>
       </c>
       <c r="L106" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M106">
         <v>3</v>
       </c>
       <c r="O106" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q106" t="s">
         <v>31</v>
@@ -8144,19 +8156,19 @@
     </row>
     <row r="107" spans="1:18">
       <c r="A107" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B107" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C107" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D107" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E107" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="F107" t="s">
         <v>23</v>
@@ -8171,7 +8183,7 @@
         <v>27</v>
       </c>
       <c r="L107" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M107">
         <v>0</v>
@@ -8182,19 +8194,19 @@
     </row>
     <row r="108" spans="1:18">
       <c r="A108" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B108" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C108" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D108" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E108" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="F108" t="s">
         <v>23</v>
@@ -8209,7 +8221,7 @@
         <v>27</v>
       </c>
       <c r="L108" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M108">
         <v>0</v>
@@ -8220,40 +8232,40 @@
     </row>
     <row r="109" spans="1:18">
       <c r="A109" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B109" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C109" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D109" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E109" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="F109" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G109" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H109" t="s">
         <v>55</v>
       </c>
       <c r="J109" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L109" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M109">
         <v>0</v>
       </c>
       <c r="P109" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q109" t="s">
         <v>31</v>
@@ -8261,40 +8273,40 @@
     </row>
     <row r="110" spans="1:18">
       <c r="A110" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B110" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C110" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D110" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E110" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="F110" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G110" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H110" t="s">
         <v>55</v>
       </c>
       <c r="J110" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L110" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M110">
         <v>0</v>
       </c>
       <c r="P110" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q110" t="s">
         <v>31</v>
@@ -8302,40 +8314,40 @@
     </row>
     <row r="111" spans="1:18">
       <c r="A111" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B111" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C111" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D111" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E111" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F111" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G111" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H111" t="s">
         <v>55</v>
       </c>
       <c r="J111" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L111" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M111">
         <v>0</v>
       </c>
       <c r="P111" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q111" t="s">
         <v>31</v>
@@ -8343,40 +8355,40 @@
     </row>
     <row r="112" spans="1:18">
       <c r="A112" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B112" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C112" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D112" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E112" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F112" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G112" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H112" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J112" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L112" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M112">
         <v>0</v>
       </c>
       <c r="P112" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="Q112" t="s">
         <v>31</v>
@@ -8384,40 +8396,40 @@
     </row>
     <row r="113" spans="1:17">
       <c r="A113" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B113" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C113" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D113" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E113" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F113" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G113" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H113" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J113" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L113" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="M113">
         <v>0</v>
       </c>
       <c r="P113" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="Q113" t="s">
         <v>31</v>
@@ -8425,40 +8437,40 @@
     </row>
     <row r="114" spans="1:17">
       <c r="A114" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B114" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C114" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D114" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E114" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F114" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G114" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H114" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J114" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L114" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M114">
         <v>0</v>
       </c>
       <c r="P114" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="Q114" t="s">
         <v>31</v>
@@ -8466,40 +8478,40 @@
     </row>
     <row r="115" spans="1:17">
       <c r="A115" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B115" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C115" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D115" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E115" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F115" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G115" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H115" t="s">
         <v>55</v>
       </c>
       <c r="J115" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L115" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M115">
         <v>0</v>
       </c>
       <c r="P115" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q115" t="s">
         <v>31</v>
@@ -8507,40 +8519,40 @@
     </row>
     <row r="116" spans="1:17">
       <c r="A116" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B116" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C116" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D116" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E116" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="F116" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G116" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H116" t="s">
         <v>55</v>
       </c>
       <c r="J116" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L116" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M116">
         <v>0</v>
       </c>
       <c r="P116" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q116" t="s">
         <v>31</v>
@@ -8548,40 +8560,40 @@
     </row>
     <row r="117" spans="1:17">
       <c r="A117" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B117" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C117" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D117" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E117" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="F117" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G117" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H117" t="s">
         <v>55</v>
       </c>
       <c r="J117" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L117" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M117">
         <v>0</v>
       </c>
       <c r="P117" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q117" t="s">
         <v>31</v>
@@ -8589,40 +8601,40 @@
     </row>
     <row r="118" spans="1:17">
       <c r="A118" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B118" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C118" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D118" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E118" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F118" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G118" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H118" t="s">
         <v>55</v>
       </c>
       <c r="J118" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L118" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M118">
         <v>0</v>
       </c>
       <c r="P118" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Q118" t="s">
         <v>31</v>
@@ -8630,16 +8642,16 @@
     </row>
     <row r="119" spans="1:17">
       <c r="A119" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B119" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C119" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D119" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E119" t="s">
         <v>366</v>
@@ -8657,13 +8669,13 @@
         <v>27</v>
       </c>
       <c r="L119" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="M119">
         <v>5</v>
       </c>
       <c r="O119" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="Q119" t="s">
         <v>31</v>
@@ -8671,16 +8683,16 @@
     </row>
     <row r="120" spans="1:17">
       <c r="A120" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B120" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C120" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D120" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="E120" t="s">
         <v>366</v>
@@ -8698,7 +8710,7 @@
         <v>27</v>
       </c>
       <c r="L120" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="M120">
         <v>1</v>
@@ -8712,16 +8724,16 @@
     </row>
     <row r="121" spans="1:17">
       <c r="A121" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B121" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C121" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D121" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="E121" t="s">
         <v>366</v>
@@ -8739,7 +8751,7 @@
         <v>27</v>
       </c>
       <c r="L121" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="M121">
         <v>1</v>
